--- a/data/fleet.xlsx
+++ b/data/fleet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usafa0-my.sharepoint.com/personal/c27jakob_brunsell_afacademy_af_edu/Documents/Desktop/Howard Boats/Howard Boats Interface/Interface/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="11_AA14A4C681AF7B1BC0285D756A0C0818F5C82E72" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{661F5C35-EB0A-4659-BD17-BF40F22161BB}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="11_AA14A4C681AF7B1BC0285D756A0C0818F5C82E72" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BC1B406-1F5B-4E38-8D8F-2EAA2D76C348}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,20 @@
     <sheet name="Fleet" sheetId="1" r:id="rId1"/>
     <sheet name="Notes" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -196,7 +209,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="96">
   <si>
     <t>Hull #</t>
   </si>
@@ -463,6 +476,27 @@
   </si>
   <si>
     <t>Dan Brunsell</t>
+  </si>
+  <si>
+    <t>Ryan Guluzza</t>
+  </si>
+  <si>
+    <t>Caleb Magno</t>
+  </si>
+  <si>
+    <t>Beau Smith</t>
+  </si>
+  <si>
+    <t>Nate Lissy</t>
+  </si>
+  <si>
+    <t>Jack Atwood</t>
+  </si>
+  <si>
+    <t>Ben Brooks</t>
+  </si>
+  <si>
+    <t>Erin Brzusek</t>
   </si>
 </sst>
 </file>
@@ -1123,12 +1157,25 @@
       <c r="E8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
+      <c r="F8" s="9">
+        <f ca="1">RANDBETWEEN(0,400)</f>
+        <v>266</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
+        <v>12</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
@@ -1137,15 +1184,34 @@
       <c r="B9" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
+      <c r="C9" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="8">
+        <v>2010</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="9">
+        <f t="shared" ref="F9:F15" ca="1" si="0">RANDBETWEEN(0,400)</f>
+        <v>52</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H9" s="7">
+        <v>2</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="7">
+        <v>1</v>
+      </c>
+      <c r="K9" s="7">
+        <v>20</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
@@ -1154,15 +1220,34 @@
       <c r="B10" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
+      <c r="C10" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="8">
+        <v>2026</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="9">
+        <f t="shared" ca="1" si="0"/>
+        <v>312</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="7">
+        <v>4</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="7">
+        <v>0</v>
+      </c>
+      <c r="K10" s="7">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
@@ -1171,15 +1256,34 @@
       <c r="B11" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
+      <c r="C11" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="8">
+        <v>2017</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="9">
+        <f t="shared" ca="1" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="7">
+        <v>2</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J11" s="7">
+        <v>2</v>
+      </c>
+      <c r="K11" s="7">
+        <v>-10</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
@@ -1188,15 +1292,34 @@
       <c r="B12" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
+      <c r="C12" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="8">
+        <v>2022</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="9">
+        <f t="shared" ca="1" si="0"/>
+        <v>368</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="7">
+        <v>4</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" s="7">
+        <v>0</v>
+      </c>
+      <c r="K12" s="7">
+        <v>24</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
@@ -1205,15 +1328,34 @@
       <c r="B13" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
+      <c r="C13" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="8">
+        <v>2024</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="9">
+        <f t="shared" ca="1" si="0"/>
+        <v>359</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="7">
+        <v>2</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="7">
+        <v>0</v>
+      </c>
+      <c r="K13" s="7">
+        <v>15</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
@@ -1222,15 +1364,34 @@
       <c r="B14" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
+      <c r="C14" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="8">
+        <v>2015</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="9">
+        <f t="shared" ca="1" si="0"/>
+        <v>171</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" s="7">
+        <v>2</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="7">
+        <v>2</v>
+      </c>
+      <c r="K14" s="7">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
@@ -1239,15 +1400,34 @@
       <c r="B15" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
+      <c r="C15" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="8">
+        <v>2020</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="9">
+        <f t="shared" ca="1" si="0"/>
+        <v>172</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="7">
+        <v>4</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J15" s="7">
+        <v>4</v>
+      </c>
+      <c r="K15" s="7">
+        <v>34.9</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
